--- a/exports/WATCHLIST_trend_following.xlsx
+++ b/exports/WATCHLIST_trend_following.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,10 +471,10 @@
         <v>66.7</v>
       </c>
       <c r="E2" t="n">
-        <v>72.94</v>
+        <v>65.62</v>
       </c>
       <c r="F2" t="n">
-        <v>107.9</v>
+        <v>97.52</v>
       </c>
       <c r="G2" t="n">
         <v>6.53</v>
@@ -495,16 +495,16 @@
         <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>61.5</v>
+        <v>38.5</v>
       </c>
       <c r="E3" t="n">
-        <v>34.17</v>
+        <v>29.81</v>
       </c>
       <c r="F3" t="n">
-        <v>0.51</v>
+        <v>-0.01</v>
       </c>
       <c r="G3" t="n">
-        <v>4.4</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="4">
@@ -522,16 +522,16 @@
         <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>81.8</v>
+        <v>63.6</v>
       </c>
       <c r="E4" t="n">
-        <v>30.18</v>
+        <v>22.09</v>
       </c>
       <c r="F4" t="n">
-        <v>10.86</v>
+        <v>5.46</v>
       </c>
       <c r="G4" t="n">
-        <v>8.69</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -552,10 +552,10 @@
         <v>54.5</v>
       </c>
       <c r="E5" t="n">
-        <v>24.99</v>
+        <v>20.26</v>
       </c>
       <c r="F5" t="n">
-        <v>5.37</v>
+        <v>3.05</v>
       </c>
       <c r="G5" t="n">
         <v>7.55</v>
@@ -564,7 +564,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>DATAPATTNS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -573,25 +573,25 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D6" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="E6" t="n">
-        <v>11.51</v>
+        <v>13.26</v>
       </c>
       <c r="F6" t="n">
-        <v>4.08</v>
+        <v>1.64</v>
       </c>
       <c r="G6" t="n">
-        <v>7.82</v>
+        <v>9.82</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>KFINTECH</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -600,25 +600,25 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>58.3</v>
+        <v>53.8</v>
       </c>
       <c r="E7" t="n">
-        <v>10.29</v>
+        <v>10.46</v>
       </c>
       <c r="F7" t="n">
-        <v>1.18</v>
+        <v>0.18</v>
       </c>
       <c r="G7" t="n">
-        <v>5.01</v>
+        <v>10.71</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DELHIVERY</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -627,25 +627,25 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>63.6</v>
+        <v>50</v>
       </c>
       <c r="E8" t="n">
-        <v>9.220000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="F8" t="n">
-        <v>2.33</v>
+        <v>1.77</v>
       </c>
       <c r="G8" t="n">
-        <v>5.1</v>
+        <v>7.92</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IREDA</t>
+          <t>KFINTECH</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -654,25 +654,25 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D9" t="n">
-        <v>40</v>
+        <v>33.3</v>
       </c>
       <c r="E9" t="n">
-        <v>8.44</v>
+        <v>5.28</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1</v>
+        <v>-2.81</v>
       </c>
       <c r="G9" t="n">
-        <v>6.26</v>
+        <v>6.76</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NYKAA</t>
+          <t>DELHIVERY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -681,25 +681,25 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>46.2</v>
+        <v>36.4</v>
       </c>
       <c r="E10" t="n">
-        <v>5.5</v>
+        <v>5.24</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.35</v>
+        <v>-1.07</v>
       </c>
       <c r="G10" t="n">
-        <v>4.51</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ENRIN</t>
+          <t>IREDA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -708,25 +708,25 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="E11" t="n">
-        <v>4.4</v>
+        <v>3.59</v>
       </c>
       <c r="F11" t="n">
-        <v>3.28</v>
+        <v>-3.06</v>
       </c>
       <c r="G11" t="n">
-        <v>6.75</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>NYKAA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -735,25 +735,25 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D12" t="n">
-        <v>41.7</v>
+        <v>46.2</v>
       </c>
       <c r="E12" t="n">
-        <v>4.02</v>
+        <v>1.77</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.35</v>
+        <v>-3.33</v>
       </c>
       <c r="G12" t="n">
-        <v>4.92</v>
+        <v>5.93</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SAGILITY</t>
+          <t>MANKIND</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -762,19 +762,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>42.9</v>
+        <v>33.3</v>
       </c>
       <c r="E13" t="n">
-        <v>2.71</v>
+        <v>1.36</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.75</v>
+        <v>-4.34</v>
       </c>
       <c r="G13" t="n">
-        <v>7.14</v>
+        <v>5.77</v>
       </c>
     </row>
     <row r="14">
@@ -795,19 +795,19 @@
         <v>27.3</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2</v>
+        <v>-0.14</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.85</v>
+        <v>-4.94</v>
       </c>
       <c r="G14" t="n">
-        <v>6.13</v>
+        <v>7.31</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SWIGGY</t>
+          <t>ENRIN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -816,25 +816,25 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
         <v>50</v>
       </c>
       <c r="E15" t="n">
-        <v>1.02</v>
+        <v>-0.19</v>
       </c>
       <c r="F15" t="n">
-        <v>2.02</v>
+        <v>-0.77</v>
       </c>
       <c r="G15" t="n">
-        <v>8.27</v>
+        <v>7.52</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>VMM</t>
+          <t>SAGILITY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -843,46 +843,127 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>28.6</v>
       </c>
       <c r="E16" t="n">
-        <v>0.19</v>
+        <v>-0.77</v>
       </c>
       <c r="F16" t="n">
-        <v>-4.32</v>
+        <v>-9.529999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>9.210000000000001</v>
+        <v>9.529999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>VMM</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>20</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-1.85</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-5.65</v>
+      </c>
+      <c r="G17" t="n">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>WAAREEENER</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>7</v>
+      </c>
+      <c r="D18" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-2.14</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-2.83</v>
+      </c>
+      <c r="G18" t="n">
+        <v>9.26</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SWIGGY</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D19" t="n">
+        <v>25</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-2.81</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-2.74</v>
+      </c>
+      <c r="G19" t="n">
+        <v>8.27</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>PREMIERENE</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
         <v>8</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D20" t="n">
         <v>25</v>
       </c>
-      <c r="E17" t="n">
-        <v>-2.38</v>
-      </c>
-      <c r="F17" t="n">
-        <v>-6.97</v>
-      </c>
-      <c r="G17" t="n">
-        <v>8.970000000000001</v>
+      <c r="E20" t="n">
+        <v>-6.3</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-9.66</v>
+      </c>
+      <c r="G20" t="n">
+        <v>9.960000000000001</v>
       </c>
     </row>
   </sheetData>
